--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.99509771653072</v>
+        <v>8.449203378936241</v>
       </c>
       <c r="D2" t="n">
-        <v>25.24592662590317</v>
+        <v>4.102463076709265</v>
       </c>
       <c r="E2" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F2" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.29505668912304</v>
+        <v>5.247946711982494</v>
       </c>
       <c r="D3" t="n">
-        <v>32.74209993247329</v>
+        <v>5.320591239026911</v>
       </c>
       <c r="E3" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F3" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.02668214810827</v>
+        <v>5.854335849067595</v>
       </c>
       <c r="D4" t="n">
-        <v>14.73855343538455</v>
+        <v>2.395014933249989</v>
       </c>
       <c r="E4" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F4" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.21117883657178</v>
+        <v>8.159316560942914</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9822956480261358</v>
+        <v>0.1596230428042471</v>
       </c>
       <c r="E5" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F5" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.20409824845058</v>
+        <v>2.145665965373219</v>
       </c>
       <c r="D6" t="n">
-        <v>9.247424787763428</v>
+        <v>1.502706528011557</v>
       </c>
       <c r="E6" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F6" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.67402929710597</v>
+        <v>7.422029760779721</v>
       </c>
       <c r="D7" t="n">
-        <v>9.223725837653706</v>
+        <v>1.498855448618727</v>
       </c>
       <c r="E7" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F7" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.2996541545684</v>
+        <v>3.948693800117365</v>
       </c>
       <c r="D8" t="n">
-        <v>13.45587086826593</v>
+        <v>2.186579016093214</v>
       </c>
       <c r="E8" t="n">
-        <v>13.20849546150991</v>
+        <v>2.146380512495361</v>
       </c>
       <c r="F8" t="n">
-        <v>9.893067884251362</v>
+        <v>1.607623531190847</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
